--- a/data/trans_orig/P57B6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023</t>
+          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202942</t>
+          <t>201986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250721</t>
+          <t>249458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149807</t>
+          <t>149199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185539</t>
+          <t>184951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366218</t>
+          <t>364928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424910</t>
+          <t>424871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>173277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217342</t>
+          <t>217086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170417</t>
+          <t>169020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205057</t>
+          <t>205772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356861</t>
+          <t>354398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413449</t>
+          <t>412214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>55591</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>87583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66737</t>
+          <t>66464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94610</t>
+          <t>93390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127293</t>
+          <t>130491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>169001</t>
+          <t>173694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>171605</t>
+          <t>175355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>216845</t>
+          <t>218916</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>110496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143291</t>
+          <t>142075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>296778</t>
+          <t>296007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>353873</t>
+          <t>351750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165053</t>
+          <t>164528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209162</t>
+          <t>207260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153611</t>
+          <t>153643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186931</t>
+          <t>186689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329705</t>
+          <t>329266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>383034</t>
+          <t>384605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>45369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73095</t>
+          <t>73646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59481</t>
+          <t>59147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86067</t>
+          <t>85857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111375</t>
+          <t>111010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150370</t>
+          <t>149898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296333</t>
+          <t>293820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>582117</t>
+          <t>578769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330410</t>
+          <t>323718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>687379</t>
+          <t>690271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63526</t>
+          <t>59526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269247</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64819</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85451</t>
+          <t>85363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348466</t>
+          <t>354582</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91969</t>
+          <t>92553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134073</t>
+          <t>134904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31695</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>364864</t>
+          <t>361566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>436674</t>
+          <t>434614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139174</t>
+          <t>115138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319796</t>
+          <t>319268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>448665</t>
+          <t>444852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>731602</t>
+          <t>728646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>421012</t>
+          <t>422672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>493489</t>
+          <t>497571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427656</t>
+          <t>425248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731839</t>
+          <t>774673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>879356</t>
+          <t>880198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1334590</t>
+          <t>1305468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135342</t>
+          <t>134665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>180801</t>
+          <t>182437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87735</t>
+          <t>73370</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>202540</t>
+          <t>201721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>208129</t>
+          <t>214599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>357695</t>
+          <t>360286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,47 +2791,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>27693</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>12982</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>41798</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>1,33%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>27693</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>14011</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>40896</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31974</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>64888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>143129</t>
+          <t>143997</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>227430</t>
+          <t>228423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>304081</t>
+          <t>300338</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>403979</t>
+          <t>401098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>195916</t>
+          <t>198399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>244074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>377552</t>
+          <t>376359</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>546739</t>
+          <t>537011</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>597406</t>
+          <t>598073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>770233</t>
+          <t>775976</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58173</t>
+          <t>59650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89081</t>
+          <t>89023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130887</t>
+          <t>131504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>207092</t>
+          <t>205957</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206910</t>
+          <t>203366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283295</t>
+          <t>282956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21769</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>44167</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>33495</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114068</t>
+          <t>112601</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164545</t>
+          <t>163372</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>244299</t>
+          <t>247978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>297363</t>
+          <t>302083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>377207</t>
+          <t>375166</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>454892</t>
+          <t>450467</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60219</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109614</t>
+          <t>113132</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>277042</t>
+          <t>277388</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>329695</t>
+          <t>328689</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>351386</t>
+          <t>353499</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>424303</t>
+          <t>423090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>141746</t>
+          <t>144248</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181114</t>
+          <t>181850</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>151929</t>
+          <t>150964</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>195142</t>
+          <t>194204</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29629</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1401783</t>
+          <t>1398715</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2001642</t>
+          <t>2021259</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>867182</t>
+          <t>838052</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1150256</t>
+          <t>1145152</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2376876</t>
+          <t>2355761</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3145653</t>
+          <t>3130331</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>999222</t>
+          <t>975190</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1434249</t>
+          <t>1433058</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1562765</t>
+          <t>1565893</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2043920</t>
+          <t>2084870</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2737947</t>
+          <t>2739130</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3410452</t>
+          <t>3403942</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>323982</t>
+          <t>328972</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>473748</t>
+          <t>475007</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>559073</t>
+          <t>551825</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>745177</t>
+          <t>746248</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>956896</t>
+          <t>955897</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1185345</t>
+          <t>1198189</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>92748</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>92068</t>
+          <t>91984</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>134714</t>
+          <t>136151</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>156242</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>213659</t>
+          <t>214627</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>226398</t>
+          <t>250402</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201986</t>
+          <t>226637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249458</t>
+          <t>277168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>166982</t>
+          <t>180605</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149199</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184951</t>
+          <t>200035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>431007</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364928</t>
+          <t>399739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424871</t>
+          <t>462171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>195156</t>
+          <t>209255</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173277</t>
+          <t>185579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217086</t>
+          <t>233026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>187596</t>
+          <t>203172</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169020</t>
+          <t>185144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205772</t>
+          <t>221787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>382752</t>
+          <t>412427</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354398</t>
+          <t>380413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>412214</t>
+          <t>438828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69722</t>
+          <t>76643</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>61502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>96280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79804</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66464</t>
+          <t>75142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93390</t>
+          <t>106114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149526</t>
+          <t>166718</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>130491</t>
+          <t>146654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>191456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,67 +1099,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>28283</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>19486</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>39445</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>26479</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>18513</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>38386</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>196097</t>
+          <t>212739</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175355</t>
+          <t>192137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>234665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110496</t>
+          <t>124254</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142075</t>
+          <t>160111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>323080</t>
+          <t>354881</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>296007</t>
+          <t>327356</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>351750</t>
+          <t>385851</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>185752</t>
+          <t>197522</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164528</t>
+          <t>175825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207260</t>
+          <t>218627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>170439</t>
+          <t>185085</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153643</t>
+          <t>168938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186689</t>
+          <t>203186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>356191</t>
+          <t>382607</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329266</t>
+          <t>355433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384605</t>
+          <t>412419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58254</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>46782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73646</t>
+          <t>75830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>79139</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>65975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85857</t>
+          <t>94299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>139608</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111010</t>
+          <t>119853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149898</t>
+          <t>161245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25627</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>436524</t>
+          <t>214171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293820</t>
+          <t>193282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578769</t>
+          <t>236587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>53823</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>483586</t>
+          <t>267994</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323718</t>
+          <t>244352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>690271</t>
+          <t>295282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165834</t>
+          <t>184309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59526</t>
+          <t>162692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269368</t>
+          <t>204932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74985</t>
+          <t>84835</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64198</t>
+          <t>73320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85363</t>
+          <t>96764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>240819</t>
+          <t>269145</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93713</t>
+          <t>243992</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>354582</t>
+          <t>293633</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>54047</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>47292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92553</t>
+          <t>76039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44978</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90149</t>
+          <t>100026</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134904</t>
+          <t>119727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32005</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>833446</t>
+          <t>657446</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>833446</t>
+          <t>657446</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>833446</t>
+          <t>657446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>396817</t>
+          <t>424989</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>361566</t>
+          <t>391618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>434614</t>
+          <t>461345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>244433</t>
+          <t>270427</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115138</t>
+          <t>246365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319268</t>
+          <t>295993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>641250</t>
+          <t>695416</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>444852</t>
+          <t>652770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>728646</t>
+          <t>740840</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>457656</t>
+          <t>510014</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>422672</t>
+          <t>473353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>497571</t>
+          <t>546166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>549751</t>
+          <t>387080</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>425248</t>
+          <t>364828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>774673</t>
+          <t>417848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1007407</t>
+          <t>897094</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>880198</t>
+          <t>852406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1305468</t>
+          <t>943873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>157053</t>
+          <t>171288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134665</t>
+          <t>146537</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182437</t>
+          <t>197999</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>154753</t>
+          <t>172101</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73370</t>
+          <t>153176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>201721</t>
+          <t>193411</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>311806</t>
+          <t>343388</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>214599</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>360286</t>
+          <t>377923</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>35628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41798</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>53424</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>41472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>68656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1032816</t>
+          <t>1129646</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1032816</t>
+          <t>1129646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1032816</t>
+          <t>1129646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>976630</t>
+          <t>859676</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976630</t>
+          <t>859676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>976630</t>
+          <t>859676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2009446</t>
+          <t>1989322</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2009446</t>
+          <t>1989322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2009446</t>
+          <t>1989322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>166347</t>
+          <t>198783</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>143997</t>
+          <t>173231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>225337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>195442</t>
+          <t>218689</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147818</t>
+          <t>199343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228423</t>
+          <t>241088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>361789</t>
+          <t>417472</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>300338</t>
+          <t>385168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>401098</t>
+          <t>451268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>270395</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198399</t>
+          <t>243165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244074</t>
+          <t>295437</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>433352</t>
+          <t>375670</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>376359</t>
+          <t>352921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>537011</t>
+          <t>399481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>654013</t>
+          <t>646065</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>598073</t>
+          <t>610799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>775976</t>
+          <t>682068</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>83337</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59650</t>
+          <t>66977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89023</t>
+          <t>99804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>196416</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131504</t>
+          <t>176025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205957</t>
+          <t>215182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>250101</t>
+          <t>279753</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>203366</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282956</t>
+          <t>306251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31911</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>45161</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33495</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59114</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>837300</t>
+          <t>826545</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>837300</t>
+          <t>826545</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>837300</t>
+          <t>826545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1311064</t>
+          <t>1393430</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1311064</t>
+          <t>1393430</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1311064</t>
+          <t>1393430</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>139707</t>
+          <t>144223</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112601</t>
+          <t>121837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163372</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>272035</t>
+          <t>298947</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>247978</t>
+          <t>271867</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>302083</t>
+          <t>326722</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>411742</t>
+          <t>443169</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>375166</t>
+          <t>401800</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>450467</t>
+          <t>479395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>84541</t>
+          <t>74365</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113132</t>
+          <t>96033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>343020</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>277388</t>
+          <t>314772</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>328689</t>
+          <t>371806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>388056</t>
+          <t>417386</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>353499</t>
+          <t>383659</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>423090</t>
+          <t>453980</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>161541</t>
+          <t>175833</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144248</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181850</t>
+          <t>199051</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,22 +3866,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>171612</t>
+          <t>188613</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>150964</t>
+          <t>163109</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>194204</t>
+          <t>211809</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29629</t>
+          <t>33096</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>235765</t>
+          <t>233102</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>235765</t>
+          <t>233102</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>235765</t>
+          <t>233102</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>757076</t>
+          <t>839622</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>757076</t>
+          <t>839622</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>757076</t>
+          <t>839622</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>992841</t>
+          <t>1072724</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>992841</t>
+          <t>1072724</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>992841</t>
+          <t>1072724</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1561891</t>
+          <t>1445306</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1398715</t>
+          <t>1385497</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2021259</t>
+          <t>1504999</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1052937</t>
+          <t>1164633</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>838052</t>
+          <t>1112325</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1145152</t>
+          <t>1217528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2614828</t>
+          <t>2609940</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2355761</t>
+          <t>2526032</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3130331</t>
+          <t>2691460</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1309601</t>
+          <t>1445860</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>975190</t>
+          <t>1384575</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1433058</t>
+          <t>1510133</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1719637</t>
+          <t>1578862</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1565893</t>
+          <t>1529125</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2084870</t>
+          <t>1637699</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3029239</t>
+          <t>3024723</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2739130</t>
+          <t>2941013</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3403942</t>
+          <t>3104031</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>422653</t>
+          <t>464828</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>328972</t>
+          <t>418945</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>475007</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>680435</t>
+          <t>753278</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>551825</t>
+          <t>709163</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>746248</t>
+          <t>794632</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1103088</t>
+          <t>1218106</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>955897</t>
+          <t>1156232</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1198189</t>
+          <t>1275122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>61488</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>97693</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>91984</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>136151</t>
+          <t>145639</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>186572</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>152519</t>
+          <t>179307</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>214627</t>
+          <t>236117</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3366487</t>
+          <t>3433546</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3366487</t>
+          <t>3433546</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3366487</t>
+          <t>3433546</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3567240</t>
+          <t>3624164</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3567240</t>
+          <t>3624164</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3567240</t>
+          <t>3624164</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6933727</t>
+          <t>7057710</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6933727</t>
+          <t>7057710</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6933727</t>
+          <t>7057710</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
